--- a/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4A1B89-A4BD-446B-99C7-9CA8AE903EEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FC3DF56-35EE-4D55-BF29-398DA855D357}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19E82F95-5209-4575-944D-049D8FC005C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE515A49-42BA-4664-B674-4B57E981C167}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D039A2D0-DA25-4D4B-9684-C2339512AFCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44A403F4-B870-4FD1-9044-7363F24928DA}"/>
 </file>